--- a/historico/sesc_musica_capital_2026_08.xlsx
+++ b/historico/sesc_musica_capital_2026_08.xlsx
@@ -515,7 +515,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extraído em: 10/08/2026 17:35   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
+          <t>Extraído em: 25/08/2026 12:37   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
         </is>
       </c>
     </row>

--- a/historico/sesc_musica_capital_2026_08.xlsx
+++ b/historico/sesc_musica_capital_2026_08.xlsx
@@ -515,7 +515,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extraído em: 25/08/2026 12:37   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
+          <t>Extraído em: 30/08/2026 16:06   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
         </is>
       </c>
     </row>
